--- a/proyectos_diseno/BASES_DE_DATOS/Periodos_Etapas.xlsx
+++ b/proyectos_diseno/BASES_DE_DATOS/Periodos_Etapas.xlsx
@@ -3062,7 +3062,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">

--- a/proyectos_diseno/BASES_DE_DATOS/Periodos_Etapas.xlsx
+++ b/proyectos_diseno/BASES_DE_DATOS/Periodos_Etapas.xlsx
@@ -3268,12 +3268,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>3e7538c1-2613-464d-83a9-dbe30ca66836</t>
+          <t>1a76356f-f8ec-4a78-9d6e-10a971d454c3</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>e8d5b147-bd6c-4108-9796-c97cd20a32b4</t>
+          <t>53103afd-00df-4b44-83cd-6f0b650262cd</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
@@ -3296,20 +3296,20 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>fba5d7c3-d0e7-4a06-b0b4-ddec55867675</t>
+          <t>9c22973b-d525-4722-af6d-f68a927793fd</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>e8d5b147-bd6c-4108-9796-c97cd20a32b4</t>
+          <t>53103afd-00df-4b44-83cd-6f0b650262cd</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -3318,31 +3318,31 @@
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>42c7f23b-88f5-4fd9-bdd1-0d63bb9c111a</t>
+          <t>871710c5-4f12-490b-9f3c-cf8b49db8768</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>e8d5b147-bd6c-4108-9796-c97cd20a32b4</t>
+          <t>0be77874-a96f-4e1b-9b87-5fe91576eef6</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F103" s="2" t="n">
@@ -3352,12 +3352,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>fc0b77f1-e7ed-4b20-817a-1fe0d81806cd</t>
+          <t>2f1a8144-bbf3-4dc3-9930-437f29d421d9</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>e8d5b147-bd6c-4108-9796-c97cd20a32b4</t>
+          <t>0be77874-a96f-4e1b-9b87-5fe91576eef6</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
@@ -3365,27 +3365,27 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>342dbd99-6c94-46a1-95f1-f089b6d3fd75</t>
+          <t>9a566a6d-62d7-41de-900b-ab632eb6d8ac</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>e8d5b147-bd6c-4108-9796-c97cd20a32b4</t>
+          <t>0be77874-a96f-4e1b-9b87-5fe91576eef6</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F105" s="2" t="n">
@@ -3408,12 +3408,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>0dc61dfa-9814-4abb-9037-69c61a2734c6</t>
+          <t>de0c44bb-5a82-48d9-ad80-b5d4b78414d8</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>e8d5b147-bd6c-4108-9796-c97cd20a32b4</t>
+          <t>0be77874-a96f-4e1b-9b87-5fe91576eef6</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F106" s="2" t="n">
@@ -3436,12 +3436,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>1a76356f-f8ec-4a78-9d6e-10a971d454c3</t>
+          <t>18b84bfd-c60c-47a1-8904-a51e6bdb1818</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>53103afd-00df-4b44-83cd-6f0b650262cd</t>
+          <t>17857265-f42e-43f6-9a73-f15f0afa10d5</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
@@ -3464,12 +3464,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>9c22973b-d525-4722-af6d-f68a927793fd</t>
+          <t>2e632b14-0a4e-4b4c-a27b-dc41fa4355f8</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>53103afd-00df-4b44-83cd-6f0b650262cd</t>
+          <t>17857265-f42e-43f6-9a73-f15f0afa10d5</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
@@ -3492,25 +3492,25 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>871710c5-4f12-490b-9f3c-cf8b49db8768</t>
+          <t>8da5c2e7-b4b4-439e-93bb-6f703154ffe9</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>0be77874-a96f-4e1b-9b87-5fe91576eef6</t>
+          <t>17857265-f42e-43f6-9a73-f15f0afa10d5</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
@@ -3520,25 +3520,25 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>2f1a8144-bbf3-4dc3-9930-437f29d421d9</t>
+          <t>7507625f-26e8-42d9-a7ff-0837a9f3f283</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>0be77874-a96f-4e1b-9b87-5fe91576eef6</t>
+          <t>17857265-f42e-43f6-9a73-f15f0afa10d5</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
@@ -3548,25 +3548,25 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>9a566a6d-62d7-41de-900b-ab632eb6d8ac</t>
+          <t>295f9e48-fc03-4ea4-a190-c18eaa54972b</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>0be77874-a96f-4e1b-9b87-5fe91576eef6</t>
+          <t>cc7937c0-f92c-485c-bde5-1c82b9ca7646</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F111" s="2" t="n">
@@ -3576,25 +3576,25 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>de0c44bb-5a82-48d9-ad80-b5d4b78414d8</t>
+          <t>3e7538c1-2613-464d-83a9-dbe30ca66836</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>0be77874-a96f-4e1b-9b87-5fe91576eef6</t>
+          <t>e8d5b147-bd6c-4108-9796-c97cd20a32b4</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F112" s="2" t="n">
@@ -3604,12 +3604,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>18b84bfd-c60c-47a1-8904-a51e6bdb1818</t>
+          <t>fba5d7c3-d0e7-4a06-b0b4-ddec55867675</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>17857265-f42e-43f6-9a73-f15f0afa10d5</t>
+          <t>e8d5b147-bd6c-4108-9796-c97cd20a32b4</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
@@ -3617,27 +3617,27 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>2e632b14-0a4e-4b4c-a27b-dc41fa4355f8</t>
+          <t>42c7f23b-88f5-4fd9-bdd1-0d63bb9c111a</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>17857265-f42e-43f6-9a73-f15f0afa10d5</t>
+          <t>e8d5b147-bd6c-4108-9796-c97cd20a32b4</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="F114" s="2" t="n">
@@ -3660,44 +3660,44 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>8da5c2e7-b4b4-439e-93bb-6f703154ffe9</t>
+          <t>fc0b77f1-e7ed-4b20-817a-1fe0d81806cd</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>17857265-f42e-43f6-9a73-f15f0afa10d5</t>
+          <t>e8d5b147-bd6c-4108-9796-c97cd20a32b4</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>7507625f-26e8-42d9-a7ff-0837a9f3f283</t>
+          <t>342dbd99-6c94-46a1-95f1-f089b6d3fd75</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>17857265-f42e-43f6-9a73-f15f0afa10d5</t>
+          <t>e8d5b147-bd6c-4108-9796-c97cd20a32b4</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
@@ -3716,25 +3716,25 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>295f9e48-fc03-4ea4-a190-c18eaa54972b</t>
+          <t>0dc61dfa-9814-4abb-9037-69c61a2734c6</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>cc7937c0-f92c-485c-bde5-1c82b9ca7646</t>
+          <t>e8d5b147-bd6c-4108-9796-c97cd20a32b4</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F117" s="2" t="n">
